--- a/week-02/Ex2A_events_normalized.xlsx
+++ b/week-02/Ex2A_events_normalized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimmy\OneDrive\Desktop\DataAnalytics\week-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD824941-BDA8-46B7-92B1-CC06AB7AF4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29CD0C22-A331-4E30-93FF-CBE30AE47C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="11956" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
+    <workbookView xWindow="1778" yWindow="0" windowWidth="15660" windowHeight="11760" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
   </bookViews>
   <sheets>
     <sheet name="events_sample" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="132">
   <si>
     <t>Event ID</t>
   </si>
@@ -425,7 +425,10 @@
     <t>events</t>
   </si>
   <si>
-    <t>Primary_ID</t>
+    <t>Location_ID</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -930,16 +933,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
@@ -948,6 +947,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1324,16 +1326,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA38BEC-78EC-44DC-83F3-AA711D021920}">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.1328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.3984375" bestFit="1" customWidth="1"/>
@@ -1985,25 +1987,26 @@
     <row r="14" spans="1:17" s="2" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="15" spans="1:17" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="8" t="s">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B17" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E17" t="s">
@@ -2012,9 +2015,12 @@
       <c r="F17" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="9">
+      <c r="G17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B18" s="7">
         <v>102</v>
       </c>
       <c r="C18" t="s">
@@ -2029,9 +2035,12 @@
       <c r="F18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="9">
+      <c r="G18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B19" s="7">
         <v>103</v>
       </c>
       <c r="C19" t="s">
@@ -2046,9 +2055,12 @@
       <c r="F19" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="9">
+      <c r="G19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B20" s="7">
         <v>104</v>
       </c>
       <c r="C20" t="s">
@@ -2063,9 +2075,12 @@
       <c r="F20" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="9">
+      <c r="G20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B21" s="7">
         <v>105</v>
       </c>
       <c r="C21" t="s">
@@ -2080,9 +2095,12 @@
       <c r="F21" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B22" s="9">
+      <c r="G21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B22" s="7">
         <v>106</v>
       </c>
       <c r="C22" t="s">
@@ -2097,9 +2115,12 @@
       <c r="F22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B23" s="9">
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B23" s="7">
         <v>107</v>
       </c>
       <c r="C23" t="s">
@@ -2114,9 +2135,12 @@
       <c r="F23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B24" s="9">
+      <c r="G23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B24" s="7">
         <v>108</v>
       </c>
       <c r="C24" t="s">
@@ -2131,9 +2155,12 @@
       <c r="F24" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B25" s="9">
+      <c r="G24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B25" s="7">
         <v>109</v>
       </c>
       <c r="C25" t="s">
@@ -2148,9 +2175,12 @@
       <c r="F25" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B26" s="9">
+      <c r="G25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B26" s="7">
         <v>110</v>
       </c>
       <c r="C26" t="s">
@@ -2165,9 +2195,12 @@
       <c r="F26" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B27" s="9">
+      <c r="G26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B27" s="7">
         <v>111</v>
       </c>
       <c r="C27" t="s">
@@ -2182,9 +2215,12 @@
       <c r="F27" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B28" s="9">
+      <c r="G27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B28" s="7">
         <v>112</v>
       </c>
       <c r="C28" t="s">
@@ -2199,328 +2235,335 @@
       <c r="F28" t="s">
         <v>20</v>
       </c>
+      <c r="G28" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B35" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" t="s">
+        <v>46</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B36" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B37" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" t="s">
+        <v>56</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B38" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G38" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B39" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" t="s">
+        <v>63</v>
+      </c>
+      <c r="G39" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B40" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B41" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" t="s">
+        <v>74</v>
+      </c>
+      <c r="H41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B42" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s">
+        <v>80</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B43" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B44" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B45" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G45" t="s">
+        <v>89</v>
+      </c>
+      <c r="H45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B51" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B35" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35" t="s">
-        <v>46</v>
-      </c>
-      <c r="G35" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B36" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G36" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B37" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C37" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37" t="s">
-        <v>53</v>
-      </c>
-      <c r="H37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B38" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B39" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" t="s">
-        <v>66</v>
-      </c>
-      <c r="E39" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" t="s">
-        <v>68</v>
-      </c>
-      <c r="G39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B40" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40" t="s">
-        <v>57</v>
-      </c>
-      <c r="H40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B41" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" t="s">
-        <v>72</v>
-      </c>
-      <c r="E41" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" t="s">
-        <v>74</v>
-      </c>
-      <c r="G41" t="s">
-        <v>69</v>
-      </c>
-      <c r="H41" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B42" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C42" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" t="s">
-        <v>79</v>
-      </c>
-      <c r="F42" t="s">
-        <v>80</v>
-      </c>
-      <c r="G42" t="s">
-        <v>75</v>
-      </c>
-      <c r="H42" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B43" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" t="s">
-        <v>46</v>
-      </c>
-      <c r="G43" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B44" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44" t="s">
-        <v>82</v>
-      </c>
-      <c r="F44" t="s">
-        <v>83</v>
-      </c>
-      <c r="G44" t="s">
-        <v>81</v>
-      </c>
-      <c r="H44" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B45" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C45" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" t="s">
-        <v>87</v>
-      </c>
-      <c r="E45" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" t="s">
-        <v>89</v>
-      </c>
-      <c r="G45" t="s">
-        <v>84</v>
-      </c>
-      <c r="H45" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A50" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>130</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B52">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B52" s="5">
         <v>1</v>
       </c>
       <c r="C52" t="s">
@@ -2535,9 +2578,12 @@
       <c r="F52">
         <v>90026</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B53">
+      <c r="G52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B53" s="5">
         <v>2</v>
       </c>
       <c r="C53" t="s">
@@ -2552,9 +2598,12 @@
       <c r="F53">
         <v>78741</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B54">
+      <c r="G53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B54" s="5">
         <v>3</v>
       </c>
       <c r="C54" t="s">
@@ -2569,9 +2618,12 @@
       <c r="F54">
         <v>90046</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B55">
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B55" s="5">
         <v>4</v>
       </c>
       <c r="C55" t="s">
@@ -2586,9 +2638,12 @@
       <c r="F55">
         <v>60616</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B56">
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B56" s="5">
         <v>5</v>
       </c>
       <c r="C56" t="s">
@@ -2603,9 +2658,12 @@
       <c r="F56">
         <v>10011</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B57">
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B57" s="5">
         <v>6</v>
       </c>
       <c r="C57" t="s">
@@ -2620,9 +2678,12 @@
       <c r="F57">
         <v>60616</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B58">
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B58" s="5">
         <v>7</v>
       </c>
       <c r="C58" t="s">
@@ -2637,9 +2698,12 @@
       <c r="F58">
         <v>97214</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B59">
+      <c r="G58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B59" s="5">
         <v>8</v>
       </c>
       <c r="C59" t="s">
@@ -2654,9 +2718,12 @@
       <c r="F59">
         <v>48226</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B60">
+      <c r="G59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B60" s="5">
         <v>9</v>
       </c>
       <c r="C60" t="s">
@@ -2671,9 +2738,12 @@
       <c r="F60">
         <v>90026</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B61">
+      <c r="G60" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B61" s="5">
         <v>10</v>
       </c>
       <c r="C61" t="s">
@@ -2688,9 +2758,12 @@
       <c r="F61">
         <v>10012</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B62">
+      <c r="G61" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B62" s="5">
         <v>11</v>
       </c>
       <c r="C62" t="s">
@@ -2705,36 +2778,130 @@
       <c r="F62">
         <v>33132</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A67" s="4" t="s">
+      <c r="G62" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B67" s="3"/>
+      <c r="B67" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="8"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B68" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B69" s="5">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B70" s="5">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B71" s="5">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B72" s="5">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B73" s="5">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B74" s="5">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B75" s="5">
+        <v>5</v>
+      </c>
+      <c r="C75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B76" s="5">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B77" s="5">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B78" s="5">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B79" s="5">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J19:J29">
     <sortCondition ref="J19:J29"/>
   </sortState>
-  <mergeCells count="3">
-    <mergeCell ref="B16:F16"/>
+  <mergeCells count="4">
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B16:G16"/>
     <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B50:G50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CA5D0A6329BB324E86983B32928CFC2E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d7eac4bce3bbb09c82bd908806be82e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xmlns:ns3="ced60a7f-99b1-48d2-b555-34851c8026ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb51570e5b7cb8bd524bc2df5324d4a3" ns2:_="" ns3:_="">
     <xsd:import namespace="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
@@ -2975,6 +3142,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2987,14 +3163,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6414E68-BBC1-4A96-B078-EF7EE95D29CE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3013,6 +3181,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
   <ds:schemaRefs>
